--- a/autostrom/20260817_Autostrom_LKWLaden_Anforderungen_mit_Bieterfragenkatalog.xlsx
+++ b/autostrom/20260817_Autostrom_LKWLaden_Anforderungen_mit_Bieterfragenkatalog.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7987" uniqueCount="4206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="4210">
   <si>
     <t xml:space="preserve">Cockpit – Anforderungen Autostrom / LKW-Laden</t>
   </si>
@@ -13185,13 +13185,19 @@
     <t xml:space="preserve">Schnittstelle: zählt Anforderungen, die alle genannten Komponenten betreffen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Organigramm – automatische Struktur- und Statusansicht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SmartInfra → Vergabeeinheit → Partner → Art → Komponente. Jede Box rechnet direkt aus der Tabelle oberhalb; die Farbe folgt dem Komponentenstatus. Hinweis: Die Tabelle nach Vergabeeinheit, Partner und Art sortieren, damit die Gruppierung sauber zusammenfällt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">│</t>
+    <t xml:space="preserve">Organigramm – Vergabe- und Komponentenstruktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Textquellen Organigramm (Formeln – bitte nicht löschen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SmartInfra → Vergabeeinheit → Partner → Art → Komponente. Die Beschriftung jeder Box ist mit einer Formelzelle verknüpft (Spalte M) und aktualisiert sich automatisch, sobald sich Name, Anzahl oder Status in der Tabelle oberhalb ändern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statusansicht – dieselbe Struktur mit automatischer Statusfarbe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ergänzung zum Organigramm: Diese Ansicht färbt sich über bedingte Formatierung automatisch nach dem Komponentenstatus und passt sich auch einer Umsortierung der Tabelle an.</t>
   </si>
   <si>
     <t xml:space="preserve">Legende Statusfarben</t>
@@ -13200,7 +13206,7 @@
     <t xml:space="preserve">keine Anforderungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Pflegehinweis: Es werden ausschließlich Vergabeeinheit, Partner, Art, Komponente und Bemerkung eingetragen. Anzahl, Statusverteilung, Gesamtstatus und das gesamte Organigramm aktualisieren sich daraus automatisch. „Zuordnung prüfen“ bedeutet: aus den vorliegenden Unterlagen nicht eindeutig ableitbar.</t>
+    <t xml:space="preserve">Pflegehinweis: Es werden ausschließlich Vergabeeinheit, Partner, Art, Komponente und Bemerkung eingetragen. Anzahl, Statusverteilung, Gesamtstatus, die Beschriftung der Organigramm-Boxen und die Statusansicht aktualisieren sich daraus automatisch. Kommen Komponenten hinzu oder ändert sich die Gruppierung, muss die Boxenanordnung des Organigramms neu erzeugt werden. „Zuordnung prüfen“ bedeutet: aus den vorliegenden Unterlagen nicht eindeutig ableitbar.</t>
   </si>
   <si>
     <t xml:space="preserve">Lesehilfe – Anforderungen</t>
@@ -13314,7 +13320,13 @@
     <t xml:space="preserve">Organigramm</t>
   </si>
   <si>
-    <t xml:space="preserve">Im Register „Komponenten“ unterhalb der Tabelle: SmartInfra → Vergabeeinheit → Partner → Art → Komponente. Vollständig formelbasiert, Farbe je Komponentenstatus. Tabelle nach Vergabeeinheit, Partner und Art sortieren.</t>
+    <t xml:space="preserve">Im Register „Komponenten“ unterhalb der Tabelle: SmartInfra → Vergabeeinheit → Partner → Art → Komponente, gezeichnet mit Excel-Zeichenobjekten. Die Beschriftung jeder Box ist über die Bearbeitungsleiste mit einer Formelzelle in Spalte M verknüpft und aktualisiert sich automatisch. Die Boxenanordnung selbst ist fest; kommen Komponenten hinzu oder ändert sich die Gruppierung, muss sie neu erzeugt werden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statusansicht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unterhalb des Organigramms, gleiche Hierarchie in Zellen. Sie färbt sich über bedingte Formatierung automatisch nach dem Komponentenstatus und passt sich auch einer Umsortierung der Tabelle ohne Nacharbeit an.</t>
   </si>
 </sst>
 </file>
@@ -13329,7 +13341,7 @@
     <numFmt numFmtId="168" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13525,15 +13537,23 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="8"/>
       <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -13592,7 +13612,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -13667,12 +13687,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF1F3A63"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
@@ -13690,7 +13704,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -13705,19 +13719,6 @@
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
@@ -13756,7 +13757,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -13977,51 +13978,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14029,11 +14034,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="7" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="7" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14045,7 +14050,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14459,11 +14464,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="73572444"/>
-        <c:axId val="80458379"/>
+        <c:axId val="58011346"/>
+        <c:axId val="55536846"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="73572444"/>
+        <c:axId val="58011346"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14507,7 +14512,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80458379"/>
+        <c:crossAx val="55536846"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14515,7 +14520,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80458379"/>
+        <c:axId val="55536846"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14559,7 +14564,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73572444"/>
+        <c:crossAx val="58011346"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14761,11 +14766,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="92475459"/>
-        <c:axId val="20549645"/>
+        <c:axId val="76015431"/>
+        <c:axId val="23332603"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92475459"/>
+        <c:axId val="76015431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14809,7 +14814,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20549645"/>
+        <c:crossAx val="23332603"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14817,7 +14822,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20549645"/>
+        <c:axId val="23332603"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14861,7 +14866,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92475459"/>
+        <c:crossAx val="76015431"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14951,6 +14956,3311 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5753100" y="11830050"/>
+    <xdr:ext cx="2857500" cy="495300"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$34">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Organigramm 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5753100" y="11830050"/>
+          <a:ext cx="2857500" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="1F3864"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00003DDE-1B1B-4E4E-9A9A-000000033232}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>SMARTINFRA
+18 Komponenten / Schnittstellen</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5943600" y="12649200"/>
+    <xdr:ext cx="2476500" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$35">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Organigramm 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5943600" y="12649200"/>
+          <a:ext cx="2476500" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="1F4E78"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00005CCD-1B1B-4E4E-9A9A-00000004CB4B}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Zuordnung prüfen
+18 Komponenten</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="57150" y="13411200"/>
+    <xdr:ext cx="1905000" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$36">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Organigramm 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="57150" y="13411200"/>
+          <a:ext cx="1905000" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E75B6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00007BBC-1B1B-4E4E-9A9A-000000066464}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Aplitronic
+1 Komponente</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2114550" y="13411200"/>
+    <xdr:ext cx="1905000" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$37">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Organigramm 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2114550" y="13411200"/>
+          <a:ext cx="1905000" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E75B6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00009AAB-1B1B-4E4E-9A9A-00000007FD7D}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>eRound
+4 Komponenten</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4171950" y="13411200"/>
+    <xdr:ext cx="1905000" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$38">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Organigramm 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4171950" y="13411200"/>
+          <a:ext cx="1905000" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E75B6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0000B99A-1B1B-4E4E-9A9A-000000099696}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Reservierungsplattform
+2 Komponenten</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6229350" y="13411200"/>
+    <xdr:ext cx="1905000" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$39">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Organigramm 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6229350" y="13411200"/>
+          <a:ext cx="1905000" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E75B6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0000D889-1B1B-4E4E-9A9A-0000000B2FAF}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>SCS
+5 Komponenten</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8286750" y="13411200"/>
+    <xdr:ext cx="1905000" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$40">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Organigramm 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8286750" y="13411200"/>
+          <a:ext cx="1905000" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E75B6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0000F778-1B1B-4E4E-9A9A-0000000CC8C8}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>tbd
+2 Komponenten</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10344150" y="13411200"/>
+    <xdr:ext cx="1905000" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$41">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Organigramm 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10344150" y="13411200"/>
+          <a:ext cx="1905000" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E75B6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00011667-1B1B-4E4E-9A9A-0000000E61E1}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>eRound / SCS
+3 Komponenten</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="12401550" y="13411200"/>
+    <xdr:ext cx="1905000" cy="457200"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$42">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Organigramm 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12401550" y="13411200"/>
+          <a:ext cx="1905000" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E75B6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00013556-1B1B-4E4E-9A9A-0000000FFAFA}" type="TxLink">
+            <a:rPr lang="de-DE" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>eRound / tbd
+1 Komponente</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="247650" y="14173200"/>
+    <xdr:ext cx="1524000" cy="304800"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$43">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Organigramm 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="247650" y="14173200"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BDD7EE"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00015445-1B1B-4E4E-9A9A-000000119413}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Komponente
+1 Eintrag</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2305050" y="14173200"/>
+    <xdr:ext cx="1524000" cy="304800"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$45">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Organigramm 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2305050" y="14173200"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BDD7EE"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00017334-1B1B-4E4E-9A9A-000000132D2C}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Komponente
+4 Einträge</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4362450" y="14173200"/>
+    <xdr:ext cx="1524000" cy="304800"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$50">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Organigramm 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4362450" y="14173200"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BDD7EE"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00019223-1B1B-4E4E-9A9A-00000014C645}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Komponente
+2 Einträge</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6419850" y="14173200"/>
+    <xdr:ext cx="1524000" cy="304800"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$53">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Organigramm 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6419850" y="14173200"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BDD7EE"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0001B112-1B1B-4E4E-9A9A-000000165F5E}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Komponente
+5 Einträge</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8477250" y="14173200"/>
+    <xdr:ext cx="1524000" cy="304800"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$59">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Organigramm 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8477250" y="14173200"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BDD7EE"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0001D001-1B1B-4E4E-9A9A-00000017F877}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Komponente
+2 Einträge</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10534650" y="14173200"/>
+    <xdr:ext cx="1524000" cy="304800"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$62">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Organigramm 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10534650" y="14173200"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BDD7EE"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0001EEF0-1B1B-4E4E-9A9A-000000199190}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Schnittstelle
+3 Einträge</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="12592050" y="14173200"/>
+    <xdr:ext cx="1524000" cy="304800"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$66">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Organigramm 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12592050" y="14173200"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BDD7EE"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00020DDF-1B1B-4E4E-9A9A-0000001B2AA9}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Schnittstelle
+1 Eintrag</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="14706600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$44">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Organigramm 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="285750" y="14706600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00022CCE-1B1B-4E4E-9A9A-0000001CC3C2}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Ladeeinrichtung
+67 Anforderungen · 0/67 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2343150" y="14706600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$46">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Organigramm 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2343150" y="14706600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00024BBD-1B1B-4E4E-9A9A-0000001E5CDB}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Abrechnungskomponente
+21 Anforderungen · 0/21 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2343150" y="15468600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$47">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Organigramm 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2343150" y="15468600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00026AAC-1B1B-4E4E-9A9A-0000001FF5F4}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Authentifizierungskomponente
+27 Anforderungen · 0/27 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2343150" y="16230600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$48">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Organigramm 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2343150" y="16230600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0002899B-1B1B-4E4E-9A9A-000000218F0D}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Monitoring
+7 Anforderungen · 0/7 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2343150" y="16992600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$49">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Organigramm 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2343150" y="16992600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0002A88A-1B1B-4E4E-9A9A-000000232826}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>OCPI Buchungskalender
+74 Anforderungen · 0/74 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4400550" y="14706600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$51">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Organigramm 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4400550" y="14706600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0002C779-1B1B-4E4E-9A9A-00000024C13F}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Anbindung
+3 Anforderungen · 0/3 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4400550" y="15468600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$52">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Organigramm 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4400550" y="15468600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0002E668-1B1B-4E4E-9A9A-000000265A58}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Reservierungsplattform
+12 Anforderungen · 0/12 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6457950" y="14706600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$54">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Organigramm 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6457950" y="14706600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00030557-1B1B-4E4E-9A9A-00000027F371}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Belegungsdetektion
+4 Anforderungen · 0/4 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6457950" y="15468600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$55">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Organigramm 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6457950" y="15468600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00032446-1B1B-4E4E-9A9A-000000298C8A}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Dynamische Anzeige
+8 Anforderungen · 0/8 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6457950" y="16230600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$56">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Organigramm 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6457950" y="16230600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00034335-1B1B-4E4E-9A9A-0000002B25A3}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Kennzeichenerfassung
+8 Anforderungen · 0/8 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6457950" y="16992600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$57">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Organigramm 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6457950" y="16992600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00036224-1B1B-4E4E-9A9A-0000002CBEBC}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Pönalisierungssystem
+21 Anforderungen · 0/21 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6457950" y="17754600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$58">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Organigramm 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6457950" y="17754600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00038113-1B1B-4E4E-9A9A-0000002E57D5}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Schrankensteuerung
+19 Anforderungen · 0/19 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8515350" y="14706600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$60">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Organigramm 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8515350" y="14706600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0003A002-1B1B-4E4E-9A9A-0000002FF0EE}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Beschilderung
+7 Anforderungen · 0/7 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8515350" y="15468600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$61">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Organigramm 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8515350" y="15468600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0003BEF1-1B1B-4E4E-9A9A-000000318A07}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Schrankenanlage
+20 Anforderungen · 0/20 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10572750" y="14706600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$63">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Organigramm 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10572750" y="14706600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0003DDE0-1B1B-4E4E-9A9A-000000332320}" type="TxLink">
+            <a:rPr lang="de-DE" sz="700" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>OCPI Buchungskalender / Abrechnungskomponente / Belegungsdetektion / Pönalisierungssystem
+1 Anforderung · 0/1 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10572750" y="15468600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$64">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Organigramm 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10572750" y="15468600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{0003FCCF-1B1B-4E4E-9A9A-00000034BC39}" type="TxLink">
+            <a:rPr lang="de-DE" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>OCPI Buchungskalender / Dynamische Anzeige
+3 Anforderungen · 0/3 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10572750" y="16230600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$65">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Organigramm 34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10572750" y="16230600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00041BBE-1B1B-4E4E-9A9A-000000365552}" type="TxLink">
+            <a:rPr lang="de-DE" sz="700" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>OCPI Buchungskalender / Kennzeichenerfassung / Pönalisierungssystem
+2 Anforderungen · 0/2 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="12630150" y="14706600"/>
+    <xdr:ext cx="1676400" cy="666750"/>
+    <xdr:sp macro="" textlink="Komponenten!$M$67">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Organigramm 35"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12630150" y="14706600"/>
+          <a:ext cx="1676400" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7E6E6"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="1F4E78"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="27432" tIns="9144" rIns="27432" bIns="9144" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{00043AAD-1B1B-4E4E-9A9A-00000037EE6B}" type="TxLink">
+            <a:rPr lang="de-DE" sz="700" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>Authentifizierungskomponente / Schrankensteuerung
+6 Anforderungen · 0/6 erfüllt
+Status: erfasst</a:t>
+          </a:fld>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7172325" y="12325350"/>
+    <xdr:ext cx="19050" cy="161925"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Verbinder 36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7172325" y="12325350"/>
+          <a:ext cx="19050" cy="161925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7172325" y="12487275"/>
+    <xdr:ext cx="19050" cy="161925"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Verbinder 37"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7172325" y="12487275"/>
+          <a:ext cx="19050" cy="161925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7172325" y="13106400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Verbinder 38"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7172325" y="13106400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1009650" y="13249275"/>
+    <xdr:ext cx="12344400" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Verbinder 39"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1009650" y="13249275"/>
+          <a:ext cx="12344400" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1000125" y="13258800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Verbinder 40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1000125" y="13258800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="3057525" y="13258800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Verbinder 41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3057525" y="13258800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5114925" y="13258800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Verbinder 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5114925" y="13258800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7172325" y="13258800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Verbinder 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7172325" y="13258800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9229725" y="13258800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Verbinder 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9229725" y="13258800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11287125" y="13258800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Verbinder 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11287125" y="13258800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13344525" y="13258800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Verbinder 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13344525" y="13258800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1000125" y="13868400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Verbinder 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1000125" y="13868400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1000125" y="14020800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Verbinder 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1000125" y="14020800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="3057525" y="13868400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Verbinder 49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3057525" y="13868400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="3057525" y="14020800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Verbinder 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3057525" y="14020800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5114925" y="13868400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Verbinder 51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5114925" y="13868400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5114925" y="14020800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="Verbinder 52"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5114925" y="14020800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7172325" y="13868400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Verbinder 53"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7172325" y="13868400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7172325" y="14020800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Verbinder 54"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7172325" y="14020800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9229725" y="13868400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="Verbinder 55"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9229725" y="13868400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9229725" y="14020800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="Verbinder 56"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9229725" y="14020800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11287125" y="13868400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="Verbinder 57"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11287125" y="13868400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11287125" y="14020800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="Verbinder 58"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11287125" y="14020800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13344525" y="13868400"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="Verbinder 59"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13344525" y="13868400"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13344525" y="14020800"/>
+    <xdr:ext cx="19050" cy="152400"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Verbinder 60"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13344525" y="14020800"/>
+          <a:ext cx="19050" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="161925" y="14478000"/>
+    <xdr:ext cx="19050" cy="561975"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="Verbinder 61"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="161925" y="14478000"/>
+          <a:ext cx="19050" cy="561975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="171450" y="15030450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="Verbinder 62"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="171450" y="15030450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2219325" y="14478000"/>
+    <xdr:ext cx="19050" cy="2847975"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="Verbinder 63"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2219325" y="14478000"/>
+          <a:ext cx="19050" cy="2847975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2228850" y="15030450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="Verbinder 64"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2228850" y="15030450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2228850" y="15792450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="Verbinder 65"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2228850" y="15792450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2228850" y="16554450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="Verbinder 66"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2228850" y="16554450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2228850" y="17316450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="Verbinder 67"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2228850" y="17316450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4276725" y="14478000"/>
+    <xdr:ext cx="19050" cy="1323975"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="Verbinder 68"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4276725" y="14478000"/>
+          <a:ext cx="19050" cy="1323975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4286250" y="15030450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="69" name="Verbinder 69"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4286250" y="15030450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4286250" y="15792450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="70" name="Verbinder 70"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4286250" y="15792450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6334125" y="14478000"/>
+    <xdr:ext cx="19050" cy="3609975"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="71" name="Verbinder 71"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6334125" y="14478000"/>
+          <a:ext cx="19050" cy="3609975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6343650" y="15030450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="Verbinder 72"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6343650" y="15030450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6343650" y="15792450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="73" name="Verbinder 73"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6343650" y="15792450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6343650" y="16554450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="74" name="Verbinder 74"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6343650" y="16554450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6343650" y="17316450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="75" name="Verbinder 75"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6343650" y="17316450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6343650" y="18078450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="76" name="Verbinder 76"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6343650" y="18078450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8391525" y="14478000"/>
+    <xdr:ext cx="19050" cy="1323975"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="Verbinder 77"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8391525" y="14478000"/>
+          <a:ext cx="19050" cy="1323975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8401050" y="15030450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="78" name="Verbinder 78"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8401050" y="15030450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8401050" y="15792450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="79" name="Verbinder 79"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8401050" y="15792450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10448925" y="14478000"/>
+    <xdr:ext cx="19050" cy="2085975"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="80" name="Verbinder 80"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10448925" y="14478000"/>
+          <a:ext cx="19050" cy="2085975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="15030450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="81" name="Verbinder 81"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="15030450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="15792450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="82" name="Verbinder 82"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="15792450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="16554450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="83" name="Verbinder 83"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="16554450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="12506325" y="14478000"/>
+    <xdr:ext cx="19050" cy="561975"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="84" name="Verbinder 84"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12506325" y="14478000"/>
+          <a:ext cx="19050" cy="561975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="12515850" y="15030450"/>
+    <xdr:ext cx="114300" cy="19050"/>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="85" name="Verbinder 85"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12515850" y="15030450"/>
+          <a:ext cx="114300" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8EA9DB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
 </xdr:wsDr>
 </file>
 
@@ -45655,7 +48965,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9149FE6E-66BD-41E0-9B5C-12CFF0416B33}</x14:id>
+          <x14:id>{7DB69561-5B74-4D63-B14D-849069B280E7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -45669,7 +48979,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85951AE6-EDC2-4430-86DD-7FB0901E13DF}</x14:id>
+          <x14:id>{50B14FF5-D49B-433C-9742-926ED08D6F18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -45683,7 +48993,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3D671082-AF29-442D-8CBC-8254EED0C63F}</x14:id>
+          <x14:id>{BF8AEFA0-5570-4291-A52A-E12FAB998B7A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -45697,7 +49007,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6B502A93-B8AC-4A73-9765-987087867262}</x14:id>
+          <x14:id>{6149BCB1-737A-4C8C-B49D-B0AE25F84633}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -45713,7 +49023,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9149FE6E-66BD-41E0-9B5C-12CFF0416B33}">
+          <x14:cfRule type="dataBar" id="{7DB69561-5B74-4D63-B14D-849069B280E7}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -45724,7 +49034,7 @@
           <xm:sqref>B7:B21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{85951AE6-EDC2-4430-86DD-7FB0901E13DF}">
+          <x14:cfRule type="dataBar" id="{50B14FF5-D49B-433C-9742-926ED08D6F18}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -45735,7 +49045,7 @@
           <xm:sqref>B26:B32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3D671082-AF29-442D-8CBC-8254EED0C63F}">
+          <x14:cfRule type="dataBar" id="{BF8AEFA0-5570-4291-A52A-E12FAB998B7A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -45746,7 +49056,7 @@
           <xm:sqref>B37:B51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6B502A93-B8AC-4A73-9765-987087867262}">
+          <x14:cfRule type="dataBar" id="{6149BCB1-737A-4C8C-B49D-B0AE25F84633}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -45767,7 +49077,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="20"/>
@@ -45778,6 +49088,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45825,7 +49136,7 @@
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="30"/>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -46769,603 +50080,864 @@
       </c>
       <c r="K29" s="53"/>
     </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="54" t="s">
         <v>4162</v>
       </c>
+      <c r="M31" s="55" t="s">
+        <v>4163</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="55" t="s">
-        <v>4163</v>
-      </c>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
-    </row>
-    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="56" t="str">
-        <f aca="false">"SMARTINFRA"&amp;CHAR(10)&amp;COUNTA($D$6:$D$29)&amp;" Komponenten / Schnittstellen  ·  "&amp;SUM($E$6:$E$29)&amp;" Anforderungszuordnungen"</f>
+      <c r="A32" s="56" t="s">
+        <v>4164</v>
+      </c>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M34" s="57" t="str">
+        <f aca="false">"SMARTINFRA"&amp;CHAR(10)&amp;COUNTA($D$6:$D$29)&amp;" Komponenten / Schnittstellen"</f>
         <v>SMARTINFRA
-18 Komponenten / Schnittstellen  ·  310 Anforderungszuordnungen</v>
-      </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-    </row>
-    <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="57" t="s">
-        <v>4164</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="58" t="str">
+18 Komponenten / Schnittstellen</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M35" s="57" t="str">
+        <f aca="false">$A6&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A6)&amp;IF(COUNTIF($A$6:$A$29,$A6)=1," Komponente"," Komponenten")</f>
+        <v>Zuordnung prüfen
+18 Komponenten</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M36" s="57" t="str">
+        <f aca="false">$B6&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A6,$B$6:$B$29,$B6)&amp;IF(COUNTIFS($A$6:$A$29,$A6,$B$6:$B$29,$B6)=1," Komponente"," Komponenten")</f>
+        <v>Aplitronic
+1 Komponente</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M37" s="57" t="str">
+        <f aca="false">$B7&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A7,$B$6:$B$29,$B7)&amp;IF(COUNTIFS($A$6:$A$29,$A7,$B$6:$B$29,$B7)=1," Komponente"," Komponenten")</f>
+        <v>eRound
+4 Komponenten</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M38" s="57" t="str">
+        <f aca="false">$B11&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A11,$B$6:$B$29,$B11)&amp;IF(COUNTIFS($A$6:$A$29,$A11,$B$6:$B$29,$B11)=1," Komponente"," Komponenten")</f>
+        <v>Reservierungsplattform
+2 Komponenten</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M39" s="57" t="str">
+        <f aca="false">$B13&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A13,$B$6:$B$29,$B13)&amp;IF(COUNTIFS($A$6:$A$29,$A13,$B$6:$B$29,$B13)=1," Komponente"," Komponenten")</f>
+        <v>SCS
+5 Komponenten</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M40" s="57" t="str">
+        <f aca="false">$B18&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A18,$B$6:$B$29,$B18)&amp;IF(COUNTIFS($A$6:$A$29,$A18,$B$6:$B$29,$B18)=1," Komponente"," Komponenten")</f>
+        <v>tbd
+2 Komponenten</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M41" s="57" t="str">
+        <f aca="false">$B20&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A20,$B$6:$B$29,$B20)&amp;IF(COUNTIFS($A$6:$A$29,$A20,$B$6:$B$29,$B20)=1," Komponente"," Komponenten")</f>
+        <v>eRound / SCS
+3 Komponenten</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M42" s="57" t="str">
+        <f aca="false">$B23&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A23,$B$6:$B$29,$B23)&amp;IF(COUNTIFS($A$6:$A$29,$A23,$B$6:$B$29,$B23)=1," Komponente"," Komponenten")</f>
+        <v>eRound / tbd
+1 Komponente</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M43" s="57" t="str">
+        <f aca="false">$C6&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A6,$B$6:$B$29,$B6,$C$6:$C$29,$C6)&amp;IF(COUNTIFS($A$6:$A$29,$A6,$B$6:$B$29,$B6,$C$6:$C$29,$C6)=1," Eintrag"," Einträge")</f>
+        <v>Komponente
+1 Eintrag</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M44" s="57" t="str">
+        <f aca="false">IF($D6="","",$D6&amp;CHAR(10)&amp;$E6&amp;IF($E6=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H6&amp;"/"&amp;$E6&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J6)</f>
+        <v>Ladeeinrichtung
+67 Anforderungen · 0/67 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M45" s="57" t="str">
+        <f aca="false">$C7&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A7,$B$6:$B$29,$B7,$C$6:$C$29,$C7)&amp;IF(COUNTIFS($A$6:$A$29,$A7,$B$6:$B$29,$B7,$C$6:$C$29,$C7)=1," Eintrag"," Einträge")</f>
+        <v>Komponente
+4 Einträge</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M46" s="57" t="str">
+        <f aca="false">IF($D7="","",$D7&amp;CHAR(10)&amp;$E7&amp;IF($E7=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H7&amp;"/"&amp;$E7&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J7)</f>
+        <v>Abrechnungskomponente
+21 Anforderungen · 0/21 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M47" s="57" t="str">
+        <f aca="false">IF($D8="","",$D8&amp;CHAR(10)&amp;$E8&amp;IF($E8=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H8&amp;"/"&amp;$E8&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J8)</f>
+        <v>Authentifizierungskomponente
+27 Anforderungen · 0/27 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M48" s="57" t="str">
+        <f aca="false">IF($D9="","",$D9&amp;CHAR(10)&amp;$E9&amp;IF($E9=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H9&amp;"/"&amp;$E9&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J9)</f>
+        <v>Monitoring
+7 Anforderungen · 0/7 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M49" s="57" t="str">
+        <f aca="false">IF($D10="","",$D10&amp;CHAR(10)&amp;$E10&amp;IF($E10=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H10&amp;"/"&amp;$E10&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J10)</f>
+        <v>OCPI Buchungskalender
+74 Anforderungen · 0/74 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M50" s="57" t="str">
+        <f aca="false">$C11&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A11,$B$6:$B$29,$B11,$C$6:$C$29,$C11)&amp;IF(COUNTIFS($A$6:$A$29,$A11,$B$6:$B$29,$B11,$C$6:$C$29,$C11)=1," Eintrag"," Einträge")</f>
+        <v>Komponente
+2 Einträge</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M51" s="57" t="str">
+        <f aca="false">IF($D11="","",$D11&amp;CHAR(10)&amp;$E11&amp;IF($E11=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H11&amp;"/"&amp;$E11&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J11)</f>
+        <v>Anbindung
+3 Anforderungen · 0/3 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M52" s="57" t="str">
+        <f aca="false">IF($D12="","",$D12&amp;CHAR(10)&amp;$E12&amp;IF($E12=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H12&amp;"/"&amp;$E12&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J12)</f>
+        <v>Reservierungsplattform
+12 Anforderungen · 0/12 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M53" s="57" t="str">
+        <f aca="false">$C13&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A13,$B$6:$B$29,$B13,$C$6:$C$29,$C13)&amp;IF(COUNTIFS($A$6:$A$29,$A13,$B$6:$B$29,$B13,$C$6:$C$29,$C13)=1," Eintrag"," Einträge")</f>
+        <v>Komponente
+5 Einträge</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M54" s="57" t="str">
+        <f aca="false">IF($D13="","",$D13&amp;CHAR(10)&amp;$E13&amp;IF($E13=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H13&amp;"/"&amp;$E13&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J13)</f>
+        <v>Belegungsdetektion
+4 Anforderungen · 0/4 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M55" s="57" t="str">
+        <f aca="false">IF($D14="","",$D14&amp;CHAR(10)&amp;$E14&amp;IF($E14=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H14&amp;"/"&amp;$E14&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J14)</f>
+        <v>Dynamische Anzeige
+8 Anforderungen · 0/8 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M56" s="57" t="str">
+        <f aca="false">IF($D15="","",$D15&amp;CHAR(10)&amp;$E15&amp;IF($E15=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H15&amp;"/"&amp;$E15&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J15)</f>
+        <v>Kennzeichenerfassung
+8 Anforderungen · 0/8 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M57" s="57" t="str">
+        <f aca="false">IF($D16="","",$D16&amp;CHAR(10)&amp;$E16&amp;IF($E16=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H16&amp;"/"&amp;$E16&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J16)</f>
+        <v>Pönalisierungssystem
+21 Anforderungen · 0/21 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M58" s="57" t="str">
+        <f aca="false">IF($D17="","",$D17&amp;CHAR(10)&amp;$E17&amp;IF($E17=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H17&amp;"/"&amp;$E17&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J17)</f>
+        <v>Schrankensteuerung
+19 Anforderungen · 0/19 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M59" s="57" t="str">
+        <f aca="false">$C18&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A18,$B$6:$B$29,$B18,$C$6:$C$29,$C18)&amp;IF(COUNTIFS($A$6:$A$29,$A18,$B$6:$B$29,$B18,$C$6:$C$29,$C18)=1," Eintrag"," Einträge")</f>
+        <v>Komponente
+2 Einträge</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M60" s="57" t="str">
+        <f aca="false">IF($D18="","",$D18&amp;CHAR(10)&amp;$E18&amp;IF($E18=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H18&amp;"/"&amp;$E18&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J18)</f>
+        <v>Beschilderung
+7 Anforderungen · 0/7 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M61" s="57" t="str">
+        <f aca="false">IF($D19="","",$D19&amp;CHAR(10)&amp;$E19&amp;IF($E19=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H19&amp;"/"&amp;$E19&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J19)</f>
+        <v>Schrankenanlage
+20 Anforderungen · 0/20 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M62" s="57" t="str">
+        <f aca="false">$C20&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A20,$B$6:$B$29,$B20,$C$6:$C$29,$C20)&amp;IF(COUNTIFS($A$6:$A$29,$A20,$B$6:$B$29,$B20,$C$6:$C$29,$C20)=1," Eintrag"," Einträge")</f>
+        <v>Schnittstelle
+3 Einträge</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M63" s="57" t="str">
+        <f aca="false">IF($D20="","",$D20&amp;CHAR(10)&amp;$E20&amp;IF($E20=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H20&amp;"/"&amp;$E20&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J20)</f>
+        <v>OCPI Buchungskalender / Abrechnungskomponente / Belegungsdetektion / Pönalisierungssystem
+1 Anforderung · 0/1 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M64" s="57" t="str">
+        <f aca="false">IF($D21="","",$D21&amp;CHAR(10)&amp;$E21&amp;IF($E21=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H21&amp;"/"&amp;$E21&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J21)</f>
+        <v>OCPI Buchungskalender / Dynamische Anzeige
+3 Anforderungen · 0/3 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M65" s="57" t="str">
+        <f aca="false">IF($D22="","",$D22&amp;CHAR(10)&amp;$E22&amp;IF($E22=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H22&amp;"/"&amp;$E22&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J22)</f>
+        <v>OCPI Buchungskalender / Kennzeichenerfassung / Pönalisierungssystem
+2 Anforderungen · 0/2 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="58" t="s">
+        <v>4165</v>
+      </c>
+      <c r="M66" s="57" t="str">
+        <f aca="false">$C23&amp;CHAR(10)&amp;COUNTIFS($A$6:$A$29,$A23,$B$6:$B$29,$B23,$C$6:$C$29,$C23)&amp;IF(COUNTIFS($A$6:$A$29,$A23,$B$6:$B$29,$B23,$C$6:$C$29,$C23)=1," Eintrag"," Einträge")</f>
+        <v>Schnittstelle
+1 Eintrag</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="56" t="s">
+        <v>4166</v>
+      </c>
+      <c r="B67" s="56"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="56"/>
+      <c r="I67" s="56"/>
+      <c r="J67" s="56"/>
+      <c r="K67" s="56"/>
+      <c r="M67" s="57" t="str">
+        <f aca="false">IF($D23="","",$D23&amp;CHAR(10)&amp;$E23&amp;IF($E23=1," Anforderung"," Anforderungen")&amp;" · "&amp;$H23&amp;"/"&amp;$E23&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J23)</f>
+        <v>Authentifizierungskomponente / Schrankensteuerung
+6 Anforderungen · 0/6 erfüllt
+Status: erfasst</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="59" t="str">
         <f aca="false">IF($D6="","",IF($A6=$A5,"",$A6&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A6)&amp;" Komponenten"))</f>
         <v>Zuordnung prüfen
 18 Komponenten</v>
       </c>
-      <c r="B36" s="59" t="str">
+      <c r="B68" s="60" t="str">
         <f aca="false">IF($D6="","",IF(AND($A6=$A5,$B6=$B5),"","└ "&amp;$B6&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A6,$B$6:$B$29,$B6)&amp;")"))</f>
         <v>└ Aplitronic  (1)</v>
       </c>
-      <c r="C36" s="59" t="str">
+      <c r="C68" s="60" t="str">
         <f aca="false">IF($D6="","",IF(AND($A6=$A5,$B6=$B5,$C6=$C5),"","└ "&amp;$C6&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A6,$B$6:$B$29,$B6,$C$6:$C$29,$C6)&amp;")"))</f>
         <v>└ Komponente  (1)</v>
       </c>
-      <c r="D36" s="60" t="str">
+      <c r="D68" s="61" t="str">
         <f aca="false">IF($D6="","","└ "&amp;$D6&amp;CHAR(10)&amp;$E6&amp;" Anforderungen  ·  "&amp;$H6&amp;"/"&amp;$E6&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J6)</f>
         <v>└ Ladeeinrichtung
 67 Anforderungen  ·  0/67 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E36" s="60"/>
-    </row>
-    <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="58" t="str">
+      <c r="E68" s="61"/>
+    </row>
+    <row r="69" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="59" t="str">
         <f aca="false">IF($D7="","",IF($A7=$A6,"",$A7&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A7)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B37" s="59" t="str">
+      <c r="B69" s="60" t="str">
         <f aca="false">IF($D7="","",IF(AND($A7=$A6,$B7=$B6),"","└ "&amp;$B7&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A7,$B$6:$B$29,$B7)&amp;")"))</f>
         <v>└ eRound  (4)</v>
       </c>
-      <c r="C37" s="59" t="str">
+      <c r="C69" s="60" t="str">
         <f aca="false">IF($D7="","",IF(AND($A7=$A6,$B7=$B6,$C7=$C6),"","└ "&amp;$C7&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A7,$B$6:$B$29,$B7,$C$6:$C$29,$C7)&amp;")"))</f>
         <v>└ Komponente  (4)</v>
       </c>
-      <c r="D37" s="60" t="str">
+      <c r="D69" s="61" t="str">
         <f aca="false">IF($D7="","","└ "&amp;$D7&amp;CHAR(10)&amp;$E7&amp;" Anforderungen  ·  "&amp;$H7&amp;"/"&amp;$E7&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J7)</f>
         <v>└ Abrechnungskomponente
 21 Anforderungen  ·  0/21 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E37" s="60"/>
-    </row>
-    <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="58" t="str">
+      <c r="E69" s="61"/>
+    </row>
+    <row r="70" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="59" t="str">
         <f aca="false">IF($D8="","",IF($A8=$A7,"",$A8&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A8)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B38" s="59" t="str">
+      <c r="B70" s="60" t="str">
         <f aca="false">IF($D8="","",IF(AND($A8=$A7,$B8=$B7),"","└ "&amp;$B8&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A8,$B$6:$B$29,$B8)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C38" s="59" t="str">
+      <c r="C70" s="60" t="str">
         <f aca="false">IF($D8="","",IF(AND($A8=$A7,$B8=$B7,$C8=$C7),"","└ "&amp;$C8&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A8,$B$6:$B$29,$B8,$C$6:$C$29,$C8)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D38" s="60" t="str">
+      <c r="D70" s="61" t="str">
         <f aca="false">IF($D8="","","└ "&amp;$D8&amp;CHAR(10)&amp;$E8&amp;" Anforderungen  ·  "&amp;$H8&amp;"/"&amp;$E8&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J8)</f>
         <v>└ Authentifizierungskomponente
 27 Anforderungen  ·  0/27 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E38" s="60"/>
-    </row>
-    <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="58" t="str">
+      <c r="E70" s="61"/>
+    </row>
+    <row r="71" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="59" t="str">
         <f aca="false">IF($D9="","",IF($A9=$A8,"",$A9&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A9)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B39" s="59" t="str">
+      <c r="B71" s="60" t="str">
         <f aca="false">IF($D9="","",IF(AND($A9=$A8,$B9=$B8),"","└ "&amp;$B9&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A9,$B$6:$B$29,$B9)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C39" s="59" t="str">
+      <c r="C71" s="60" t="str">
         <f aca="false">IF($D9="","",IF(AND($A9=$A8,$B9=$B8,$C9=$C8),"","└ "&amp;$C9&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A9,$B$6:$B$29,$B9,$C$6:$C$29,$C9)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D39" s="60" t="str">
+      <c r="D71" s="61" t="str">
         <f aca="false">IF($D9="","","└ "&amp;$D9&amp;CHAR(10)&amp;$E9&amp;" Anforderungen  ·  "&amp;$H9&amp;"/"&amp;$E9&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J9)</f>
         <v>└ Monitoring
 7 Anforderungen  ·  0/7 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E39" s="60"/>
-    </row>
-    <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="58" t="str">
+      <c r="E71" s="61"/>
+    </row>
+    <row r="72" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="59" t="str">
         <f aca="false">IF($D10="","",IF($A10=$A9,"",$A10&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A10)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B40" s="59" t="str">
+      <c r="B72" s="60" t="str">
         <f aca="false">IF($D10="","",IF(AND($A10=$A9,$B10=$B9),"","└ "&amp;$B10&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A10,$B$6:$B$29,$B10)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C40" s="59" t="str">
+      <c r="C72" s="60" t="str">
         <f aca="false">IF($D10="","",IF(AND($A10=$A9,$B10=$B9,$C10=$C9),"","└ "&amp;$C10&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A10,$B$6:$B$29,$B10,$C$6:$C$29,$C10)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D40" s="60" t="str">
+      <c r="D72" s="61" t="str">
         <f aca="false">IF($D10="","","└ "&amp;$D10&amp;CHAR(10)&amp;$E10&amp;" Anforderungen  ·  "&amp;$H10&amp;"/"&amp;$E10&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J10)</f>
         <v>└ OCPI Buchungskalender
 74 Anforderungen  ·  0/74 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E40" s="60"/>
-    </row>
-    <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58" t="str">
+      <c r="E72" s="61"/>
+    </row>
+    <row r="73" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="59" t="str">
         <f aca="false">IF($D11="","",IF($A11=$A10,"",$A11&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A11)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B41" s="59" t="str">
+      <c r="B73" s="60" t="str">
         <f aca="false">IF($D11="","",IF(AND($A11=$A10,$B11=$B10),"","└ "&amp;$B11&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A11,$B$6:$B$29,$B11)&amp;")"))</f>
         <v>└ Reservierungsplattform  (2)</v>
       </c>
-      <c r="C41" s="59" t="str">
+      <c r="C73" s="60" t="str">
         <f aca="false">IF($D11="","",IF(AND($A11=$A10,$B11=$B10,$C11=$C10),"","└ "&amp;$C11&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A11,$B$6:$B$29,$B11,$C$6:$C$29,$C11)&amp;")"))</f>
         <v>└ Komponente  (2)</v>
       </c>
-      <c r="D41" s="60" t="str">
+      <c r="D73" s="61" t="str">
         <f aca="false">IF($D11="","","└ "&amp;$D11&amp;CHAR(10)&amp;$E11&amp;" Anforderungen  ·  "&amp;$H11&amp;"/"&amp;$E11&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J11)</f>
         <v>└ Anbindung
 3 Anforderungen  ·  0/3 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E41" s="60"/>
-    </row>
-    <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="58" t="str">
+      <c r="E73" s="61"/>
+    </row>
+    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="59" t="str">
         <f aca="false">IF($D12="","",IF($A12=$A11,"",$A12&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A12)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B42" s="59" t="str">
+      <c r="B74" s="60" t="str">
         <f aca="false">IF($D12="","",IF(AND($A12=$A11,$B12=$B11),"","└ "&amp;$B12&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A12,$B$6:$B$29,$B12)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C42" s="59" t="str">
+      <c r="C74" s="60" t="str">
         <f aca="false">IF($D12="","",IF(AND($A12=$A11,$B12=$B11,$C12=$C11),"","└ "&amp;$C12&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A12,$B$6:$B$29,$B12,$C$6:$C$29,$C12)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D42" s="60" t="str">
+      <c r="D74" s="61" t="str">
         <f aca="false">IF($D12="","","└ "&amp;$D12&amp;CHAR(10)&amp;$E12&amp;" Anforderungen  ·  "&amp;$H12&amp;"/"&amp;$E12&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J12)</f>
         <v>└ Reservierungsplattform
 12 Anforderungen  ·  0/12 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E42" s="60"/>
-    </row>
-    <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="58" t="str">
+      <c r="E74" s="61"/>
+    </row>
+    <row r="75" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="59" t="str">
         <f aca="false">IF($D13="","",IF($A13=$A12,"",$A13&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A13)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B43" s="59" t="str">
+      <c r="B75" s="60" t="str">
         <f aca="false">IF($D13="","",IF(AND($A13=$A12,$B13=$B12),"","└ "&amp;$B13&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A13,$B$6:$B$29,$B13)&amp;")"))</f>
         <v>└ SCS  (5)</v>
       </c>
-      <c r="C43" s="59" t="str">
+      <c r="C75" s="60" t="str">
         <f aca="false">IF($D13="","",IF(AND($A13=$A12,$B13=$B12,$C13=$C12),"","└ "&amp;$C13&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A13,$B$6:$B$29,$B13,$C$6:$C$29,$C13)&amp;")"))</f>
         <v>└ Komponente  (5)</v>
       </c>
-      <c r="D43" s="60" t="str">
+      <c r="D75" s="61" t="str">
         <f aca="false">IF($D13="","","└ "&amp;$D13&amp;CHAR(10)&amp;$E13&amp;" Anforderungen  ·  "&amp;$H13&amp;"/"&amp;$E13&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J13)</f>
         <v>└ Belegungsdetektion
 4 Anforderungen  ·  0/4 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E43" s="60"/>
-    </row>
-    <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="58" t="str">
+      <c r="E75" s="61"/>
+    </row>
+    <row r="76" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="59" t="str">
         <f aca="false">IF($D14="","",IF($A14=$A13,"",$A14&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A14)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B44" s="59" t="str">
+      <c r="B76" s="60" t="str">
         <f aca="false">IF($D14="","",IF(AND($A14=$A13,$B14=$B13),"","└ "&amp;$B14&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A14,$B$6:$B$29,$B14)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C44" s="59" t="str">
+      <c r="C76" s="60" t="str">
         <f aca="false">IF($D14="","",IF(AND($A14=$A13,$B14=$B13,$C14=$C13),"","└ "&amp;$C14&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A14,$B$6:$B$29,$B14,$C$6:$C$29,$C14)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D44" s="60" t="str">
+      <c r="D76" s="61" t="str">
         <f aca="false">IF($D14="","","└ "&amp;$D14&amp;CHAR(10)&amp;$E14&amp;" Anforderungen  ·  "&amp;$H14&amp;"/"&amp;$E14&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J14)</f>
         <v>└ Dynamische Anzeige
 8 Anforderungen  ·  0/8 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E44" s="60"/>
-    </row>
-    <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="58" t="str">
+      <c r="E76" s="61"/>
+    </row>
+    <row r="77" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="59" t="str">
         <f aca="false">IF($D15="","",IF($A15=$A14,"",$A15&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A15)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B45" s="59" t="str">
+      <c r="B77" s="60" t="str">
         <f aca="false">IF($D15="","",IF(AND($A15=$A14,$B15=$B14),"","└ "&amp;$B15&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A15,$B$6:$B$29,$B15)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C45" s="59" t="str">
+      <c r="C77" s="60" t="str">
         <f aca="false">IF($D15="","",IF(AND($A15=$A14,$B15=$B14,$C15=$C14),"","└ "&amp;$C15&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A15,$B$6:$B$29,$B15,$C$6:$C$29,$C15)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D45" s="60" t="str">
+      <c r="D77" s="61" t="str">
         <f aca="false">IF($D15="","","└ "&amp;$D15&amp;CHAR(10)&amp;$E15&amp;" Anforderungen  ·  "&amp;$H15&amp;"/"&amp;$E15&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J15)</f>
         <v>└ Kennzeichenerfassung
 8 Anforderungen  ·  0/8 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E45" s="60"/>
-    </row>
-    <row r="46" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58" t="str">
+      <c r="E77" s="61"/>
+    </row>
+    <row r="78" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="59" t="str">
         <f aca="false">IF($D16="","",IF($A16=$A15,"",$A16&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A16)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B46" s="59" t="str">
+      <c r="B78" s="60" t="str">
         <f aca="false">IF($D16="","",IF(AND($A16=$A15,$B16=$B15),"","└ "&amp;$B16&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A16,$B$6:$B$29,$B16)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C46" s="59" t="str">
+      <c r="C78" s="60" t="str">
         <f aca="false">IF($D16="","",IF(AND($A16=$A15,$B16=$B15,$C16=$C15),"","└ "&amp;$C16&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A16,$B$6:$B$29,$B16,$C$6:$C$29,$C16)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D46" s="60" t="str">
+      <c r="D78" s="61" t="str">
         <f aca="false">IF($D16="","","└ "&amp;$D16&amp;CHAR(10)&amp;$E16&amp;" Anforderungen  ·  "&amp;$H16&amp;"/"&amp;$E16&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J16)</f>
         <v>└ Pönalisierungssystem
 21 Anforderungen  ·  0/21 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E46" s="60"/>
-    </row>
-    <row r="47" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58" t="str">
+      <c r="E78" s="61"/>
+    </row>
+    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="59" t="str">
         <f aca="false">IF($D17="","",IF($A17=$A16,"",$A17&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A17)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B47" s="59" t="str">
+      <c r="B79" s="60" t="str">
         <f aca="false">IF($D17="","",IF(AND($A17=$A16,$B17=$B16),"","└ "&amp;$B17&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A17,$B$6:$B$29,$B17)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C47" s="59" t="str">
+      <c r="C79" s="60" t="str">
         <f aca="false">IF($D17="","",IF(AND($A17=$A16,$B17=$B16,$C17=$C16),"","└ "&amp;$C17&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A17,$B$6:$B$29,$B17,$C$6:$C$29,$C17)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D47" s="60" t="str">
+      <c r="D79" s="61" t="str">
         <f aca="false">IF($D17="","","└ "&amp;$D17&amp;CHAR(10)&amp;$E17&amp;" Anforderungen  ·  "&amp;$H17&amp;"/"&amp;$E17&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J17)</f>
         <v>└ Schrankensteuerung
 19 Anforderungen  ·  0/19 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E47" s="60"/>
-    </row>
-    <row r="48" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58" t="str">
+      <c r="E79" s="61"/>
+    </row>
+    <row r="80" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="59" t="str">
         <f aca="false">IF($D18="","",IF($A18=$A17,"",$A18&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A18)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B48" s="59" t="str">
+      <c r="B80" s="60" t="str">
         <f aca="false">IF($D18="","",IF(AND($A18=$A17,$B18=$B17),"","└ "&amp;$B18&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A18,$B$6:$B$29,$B18)&amp;")"))</f>
         <v>└ tbd  (2)</v>
       </c>
-      <c r="C48" s="59" t="str">
+      <c r="C80" s="60" t="str">
         <f aca="false">IF($D18="","",IF(AND($A18=$A17,$B18=$B17,$C18=$C17),"","└ "&amp;$C18&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A18,$B$6:$B$29,$B18,$C$6:$C$29,$C18)&amp;")"))</f>
         <v>└ Komponente  (2)</v>
       </c>
-      <c r="D48" s="60" t="str">
+      <c r="D80" s="61" t="str">
         <f aca="false">IF($D18="","","└ "&amp;$D18&amp;CHAR(10)&amp;$E18&amp;" Anforderungen  ·  "&amp;$H18&amp;"/"&amp;$E18&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J18)</f>
         <v>└ Beschilderung
 7 Anforderungen  ·  0/7 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E48" s="60"/>
-    </row>
-    <row r="49" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="58" t="str">
+      <c r="E80" s="61"/>
+    </row>
+    <row r="81" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="59" t="str">
         <f aca="false">IF($D19="","",IF($A19=$A18,"",$A19&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A19)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B49" s="59" t="str">
+      <c r="B81" s="60" t="str">
         <f aca="false">IF($D19="","",IF(AND($A19=$A18,$B19=$B18),"","└ "&amp;$B19&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A19,$B$6:$B$29,$B19)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C49" s="59" t="str">
+      <c r="C81" s="60" t="str">
         <f aca="false">IF($D19="","",IF(AND($A19=$A18,$B19=$B18,$C19=$C18),"","└ "&amp;$C19&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A19,$B$6:$B$29,$B19,$C$6:$C$29,$C19)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D49" s="60" t="str">
+      <c r="D81" s="61" t="str">
         <f aca="false">IF($D19="","","└ "&amp;$D19&amp;CHAR(10)&amp;$E19&amp;" Anforderungen  ·  "&amp;$H19&amp;"/"&amp;$E19&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J19)</f>
         <v>└ Schrankenanlage
 20 Anforderungen  ·  0/20 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E49" s="60"/>
-    </row>
-    <row r="50" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="58" t="str">
+      <c r="E81" s="61"/>
+    </row>
+    <row r="82" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="59" t="str">
         <f aca="false">IF($D20="","",IF($A20=$A19,"",$A20&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A20)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B50" s="59" t="str">
+      <c r="B82" s="60" t="str">
         <f aca="false">IF($D20="","",IF(AND($A20=$A19,$B20=$B19),"","└ "&amp;$B20&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A20,$B$6:$B$29,$B20)&amp;")"))</f>
         <v>└ eRound / SCS  (3)</v>
       </c>
-      <c r="C50" s="59" t="str">
+      <c r="C82" s="60" t="str">
         <f aca="false">IF($D20="","",IF(AND($A20=$A19,$B20=$B19,$C20=$C19),"","└ "&amp;$C20&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A20,$B$6:$B$29,$B20,$C$6:$C$29,$C20)&amp;")"))</f>
         <v>└ Schnittstelle  (3)</v>
       </c>
-      <c r="D50" s="60" t="str">
+      <c r="D82" s="61" t="str">
         <f aca="false">IF($D20="","","└ "&amp;$D20&amp;CHAR(10)&amp;$E20&amp;" Anforderungen  ·  "&amp;$H20&amp;"/"&amp;$E20&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J20)</f>
         <v>└ OCPI Buchungskalender / Abrechnungskomponente / Belegungsdetektion / Pönalisierungssystem
 1 Anforderungen  ·  0/1 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E50" s="60"/>
-    </row>
-    <row r="51" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="58" t="str">
+      <c r="E82" s="61"/>
+    </row>
+    <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="59" t="str">
         <f aca="false">IF($D21="","",IF($A21=$A20,"",$A21&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A21)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B51" s="59" t="str">
+      <c r="B83" s="60" t="str">
         <f aca="false">IF($D21="","",IF(AND($A21=$A20,$B21=$B20),"","└ "&amp;$B21&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A21,$B$6:$B$29,$B21)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C51" s="59" t="str">
+      <c r="C83" s="60" t="str">
         <f aca="false">IF($D21="","",IF(AND($A21=$A20,$B21=$B20,$C21=$C20),"","└ "&amp;$C21&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A21,$B$6:$B$29,$B21,$C$6:$C$29,$C21)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D51" s="60" t="str">
+      <c r="D83" s="61" t="str">
         <f aca="false">IF($D21="","","└ "&amp;$D21&amp;CHAR(10)&amp;$E21&amp;" Anforderungen  ·  "&amp;$H21&amp;"/"&amp;$E21&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J21)</f>
         <v>└ OCPI Buchungskalender / Dynamische Anzeige
 3 Anforderungen  ·  0/3 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E51" s="60"/>
-    </row>
-    <row r="52" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="58" t="str">
+      <c r="E83" s="61"/>
+    </row>
+    <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="59" t="str">
         <f aca="false">IF($D22="","",IF($A22=$A21,"",$A22&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A22)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B52" s="59" t="str">
+      <c r="B84" s="60" t="str">
         <f aca="false">IF($D22="","",IF(AND($A22=$A21,$B22=$B21),"","└ "&amp;$B22&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A22,$B$6:$B$29,$B22)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C52" s="59" t="str">
+      <c r="C84" s="60" t="str">
         <f aca="false">IF($D22="","",IF(AND($A22=$A21,$B22=$B21,$C22=$C21),"","└ "&amp;$C22&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A22,$B$6:$B$29,$B22,$C$6:$C$29,$C22)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D52" s="60" t="str">
+      <c r="D84" s="61" t="str">
         <f aca="false">IF($D22="","","└ "&amp;$D22&amp;CHAR(10)&amp;$E22&amp;" Anforderungen  ·  "&amp;$H22&amp;"/"&amp;$E22&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J22)</f>
         <v>└ OCPI Buchungskalender / Kennzeichenerfassung / Pönalisierungssystem
 2 Anforderungen  ·  0/2 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E52" s="60"/>
-    </row>
-    <row r="53" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="58" t="str">
+      <c r="E84" s="61"/>
+    </row>
+    <row r="85" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="59" t="str">
         <f aca="false">IF($D23="","",IF($A23=$A22,"",$A23&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A23)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B53" s="59" t="str">
+      <c r="B85" s="60" t="str">
         <f aca="false">IF($D23="","",IF(AND($A23=$A22,$B23=$B22),"","└ "&amp;$B23&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A23,$B$6:$B$29,$B23)&amp;")"))</f>
         <v>└ eRound / tbd  (1)</v>
       </c>
-      <c r="C53" s="59" t="str">
+      <c r="C85" s="60" t="str">
         <f aca="false">IF($D23="","",IF(AND($A23=$A22,$B23=$B22,$C23=$C22),"","└ "&amp;$C23&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A23,$B$6:$B$29,$B23,$C$6:$C$29,$C23)&amp;")"))</f>
         <v>└ Schnittstelle  (1)</v>
       </c>
-      <c r="D53" s="60" t="str">
+      <c r="D85" s="61" t="str">
         <f aca="false">IF($D23="","","└ "&amp;$D23&amp;CHAR(10)&amp;$E23&amp;" Anforderungen  ·  "&amp;$H23&amp;"/"&amp;$E23&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J23)</f>
         <v>└ Authentifizierungskomponente / Schrankensteuerung
 6 Anforderungen  ·  0/6 erfüllt
 Status: erfasst</v>
       </c>
-      <c r="E53" s="60"/>
-    </row>
-    <row r="54" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="58" t="str">
+      <c r="E85" s="61"/>
+    </row>
+    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="59" t="str">
         <f aca="false">IF($D24="","",IF($A24=$A23,"",$A24&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A24)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B54" s="59" t="str">
+      <c r="B86" s="60" t="str">
         <f aca="false">IF($D24="","",IF(AND($A24=$A23,$B24=$B23),"","└ "&amp;$B24&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A24,$B$6:$B$29,$B24)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C54" s="59" t="str">
+      <c r="C86" s="60" t="str">
         <f aca="false">IF($D24="","",IF(AND($A24=$A23,$B24=$B23,$C24=$C23),"","└ "&amp;$C24&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A24,$B$6:$B$29,$B24,$C$6:$C$29,$C24)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D54" s="60" t="str">
+      <c r="D86" s="61" t="str">
         <f aca="false">IF($D24="","","└ "&amp;$D24&amp;CHAR(10)&amp;$E24&amp;" Anforderungen  ·  "&amp;$H24&amp;"/"&amp;$E24&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J24)</f>
         <v/>
       </c>
-      <c r="E54" s="60"/>
-    </row>
-    <row r="55" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="58" t="str">
+      <c r="E86" s="61"/>
+    </row>
+    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="59" t="str">
         <f aca="false">IF($D25="","",IF($A25=$A24,"",$A25&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A25)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B55" s="59" t="str">
+      <c r="B87" s="60" t="str">
         <f aca="false">IF($D25="","",IF(AND($A25=$A24,$B25=$B24),"","└ "&amp;$B25&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A25,$B$6:$B$29,$B25)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C55" s="59" t="str">
+      <c r="C87" s="60" t="str">
         <f aca="false">IF($D25="","",IF(AND($A25=$A24,$B25=$B24,$C25=$C24),"","└ "&amp;$C25&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A25,$B$6:$B$29,$B25,$C$6:$C$29,$C25)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D55" s="60" t="str">
+      <c r="D87" s="61" t="str">
         <f aca="false">IF($D25="","","└ "&amp;$D25&amp;CHAR(10)&amp;$E25&amp;" Anforderungen  ·  "&amp;$H25&amp;"/"&amp;$E25&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J25)</f>
         <v/>
       </c>
-      <c r="E55" s="60"/>
-    </row>
-    <row r="56" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="58" t="str">
+      <c r="E87" s="61"/>
+    </row>
+    <row r="88" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="59" t="str">
         <f aca="false">IF($D26="","",IF($A26=$A25,"",$A26&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A26)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B56" s="59" t="str">
+      <c r="B88" s="60" t="str">
         <f aca="false">IF($D26="","",IF(AND($A26=$A25,$B26=$B25),"","└ "&amp;$B26&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A26,$B$6:$B$29,$B26)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C56" s="59" t="str">
+      <c r="C88" s="60" t="str">
         <f aca="false">IF($D26="","",IF(AND($A26=$A25,$B26=$B25,$C26=$C25),"","└ "&amp;$C26&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A26,$B$6:$B$29,$B26,$C$6:$C$29,$C26)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D56" s="60" t="str">
+      <c r="D88" s="61" t="str">
         <f aca="false">IF($D26="","","└ "&amp;$D26&amp;CHAR(10)&amp;$E26&amp;" Anforderungen  ·  "&amp;$H26&amp;"/"&amp;$E26&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J26)</f>
         <v/>
       </c>
-      <c r="E56" s="60"/>
-    </row>
-    <row r="57" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="58" t="str">
+      <c r="E88" s="61"/>
+    </row>
+    <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="59" t="str">
         <f aca="false">IF($D27="","",IF($A27=$A26,"",$A27&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A27)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B57" s="59" t="str">
+      <c r="B89" s="60" t="str">
         <f aca="false">IF($D27="","",IF(AND($A27=$A26,$B27=$B26),"","└ "&amp;$B27&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A27,$B$6:$B$29,$B27)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C57" s="59" t="str">
+      <c r="C89" s="60" t="str">
         <f aca="false">IF($D27="","",IF(AND($A27=$A26,$B27=$B26,$C27=$C26),"","└ "&amp;$C27&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A27,$B$6:$B$29,$B27,$C$6:$C$29,$C27)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D57" s="60" t="str">
+      <c r="D89" s="61" t="str">
         <f aca="false">IF($D27="","","└ "&amp;$D27&amp;CHAR(10)&amp;$E27&amp;" Anforderungen  ·  "&amp;$H27&amp;"/"&amp;$E27&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J27)</f>
         <v/>
       </c>
-      <c r="E57" s="60"/>
-    </row>
-    <row r="58" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="58" t="str">
+      <c r="E89" s="61"/>
+    </row>
+    <row r="90" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="59" t="str">
         <f aca="false">IF($D28="","",IF($A28=$A27,"",$A28&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A28)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B58" s="59" t="str">
+      <c r="B90" s="60" t="str">
         <f aca="false">IF($D28="","",IF(AND($A28=$A27,$B28=$B27),"","└ "&amp;$B28&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A28,$B$6:$B$29,$B28)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C58" s="59" t="str">
+      <c r="C90" s="60" t="str">
         <f aca="false">IF($D28="","",IF(AND($A28=$A27,$B28=$B27,$C28=$C27),"","└ "&amp;$C28&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A28,$B$6:$B$29,$B28,$C$6:$C$29,$C28)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D58" s="60" t="str">
+      <c r="D90" s="61" t="str">
         <f aca="false">IF($D28="","","└ "&amp;$D28&amp;CHAR(10)&amp;$E28&amp;" Anforderungen  ·  "&amp;$H28&amp;"/"&amp;$E28&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J28)</f>
         <v/>
       </c>
-      <c r="E58" s="60"/>
-    </row>
-    <row r="59" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="58" t="str">
+      <c r="E90" s="61"/>
+    </row>
+    <row r="91" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="59" t="str">
         <f aca="false">IF($D29="","",IF($A29=$A28,"",$A29&amp;CHAR(10)&amp;COUNTIF($A$6:$A$29,$A29)&amp;" Komponenten"))</f>
         <v/>
       </c>
-      <c r="B59" s="59" t="str">
+      <c r="B91" s="60" t="str">
         <f aca="false">IF($D29="","",IF(AND($A29=$A28,$B29=$B28),"","└ "&amp;$B29&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A29,$B$6:$B$29,$B29)&amp;")"))</f>
         <v/>
       </c>
-      <c r="C59" s="59" t="str">
+      <c r="C91" s="60" t="str">
         <f aca="false">IF($D29="","",IF(AND($A29=$A28,$B29=$B28,$C29=$C28),"","└ "&amp;$C29&amp;"  ("&amp;COUNTIFS($A$6:$A$29,$A29,$B$6:$B$29,$B29,$C$6:$C$29,$C29)&amp;")"))</f>
         <v/>
       </c>
-      <c r="D59" s="60" t="str">
+      <c r="D91" s="61" t="str">
         <f aca="false">IF($D29="","","└ "&amp;$D29&amp;CHAR(10)&amp;$E29&amp;" Anforderungen  ·  "&amp;$H29&amp;"/"&amp;$E29&amp;" erfüllt"&amp;CHAR(10)&amp;"Status: "&amp;$J29)</f>
         <v/>
       </c>
-      <c r="E59" s="60"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="61" t="s">
-        <v>4165</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="62" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" s="63" t="s">
+      <c r="E91" s="61"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="62" t="s">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="B94" s="64" t="s">
         <v>4136</v>
       </c>
-      <c r="C62" s="64" t="s">
+      <c r="C94" s="65" t="s">
         <v>4137</v>
       </c>
-      <c r="D62" s="65" t="s">
+      <c r="D94" s="66" t="s">
         <v>4138</v>
       </c>
-      <c r="E62" s="66" t="s">
-        <v>4166</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="67" t="s">
-        <v>4167</v>
-      </c>
-      <c r="B64" s="67"/>
-      <c r="C64" s="67"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
-      <c r="H64" s="67"/>
-      <c r="I64" s="67"/>
-      <c r="J64" s="67"/>
-      <c r="K64" s="67"/>
+      <c r="E94" s="67" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="68" t="s">
+        <v>4169</v>
+      </c>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
+      <c r="H96" s="68"/>
+      <c r="I96" s="68"/>
+      <c r="J96" s="68"/>
+      <c r="K96" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A67:K67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A96:K96"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:E29">
     <cfRule type="dataBar" priority="2">
@@ -47376,7 +50948,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3395A58C-B1FD-4AB2-871B-EDD3D8C58935}</x14:id>
+          <x14:id>{14A653A9-E07A-4323-A77C-B11A9EF9E24B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -47403,22 +50975,22 @@
       <formula>A6="Zuordnung prüfen"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A36:A59">
+  <conditionalFormatting sqref="A68:A91">
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>$A36&lt;&gt;""</formula>
+      <formula>$A68&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B36:B59">
+  <conditionalFormatting sqref="B68:B91">
     <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>$B36&lt;&gt;""</formula>
+      <formula>$B68&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:C59">
+  <conditionalFormatting sqref="C68:C91">
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>$C36&lt;&gt;""</formula>
+      <formula>$C68&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D36:E59">
+  <conditionalFormatting sqref="D68:E91">
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>$J6="erfasst"</formula>
     </cfRule>
@@ -47442,11 +51014,12 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rIdOrga"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3395A58C-B1FD-4AB2-871B-EDD3D8C58935}">
+          <x14:cfRule type="dataBar" id="{14A653A9-E07A-4323-A77C-B11A9EF9E24B}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -47467,7 +51040,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -47476,198 +51049,206 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>4168</v>
+        <v>4170</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="68" t="s">
-        <v>4169</v>
-      </c>
-      <c r="B2" s="68"/>
+      <c r="A2" s="69" t="s">
+        <v>4171</v>
+      </c>
+      <c r="B2" s="69"/>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="s">
-        <v>4170</v>
-      </c>
-      <c r="B5" s="70" t="s">
-        <v>4171</v>
+      <c r="A5" s="70" t="s">
+        <v>4172</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>4173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="70" t="s">
         <v>4134</v>
       </c>
-      <c r="B6" s="70" t="s">
-        <v>4172</v>
+      <c r="B6" s="71" t="s">
+        <v>4174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="69" t="s">
-        <v>4173</v>
-      </c>
-      <c r="B7" s="70" t="s">
-        <v>4174</v>
+      <c r="A7" s="70" t="s">
+        <v>4175</v>
+      </c>
+      <c r="B7" s="71" t="s">
+        <v>4176</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69" t="s">
-        <v>4175</v>
-      </c>
-      <c r="B8" s="70" t="s">
-        <v>4176</v>
+      <c r="A8" s="70" t="s">
+        <v>4177</v>
+      </c>
+      <c r="B8" s="71" t="s">
+        <v>4178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="69" t="s">
-        <v>4177</v>
-      </c>
-      <c r="B9" s="70" t="s">
-        <v>4178</v>
+      <c r="A9" s="70" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B9" s="71" t="s">
+        <v>4180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="69" t="s">
-        <v>4179</v>
-      </c>
-      <c r="B10" s="70" t="s">
-        <v>4180</v>
+      <c r="A10" s="70" t="s">
+        <v>4181</v>
+      </c>
+      <c r="B10" s="71" t="s">
+        <v>4182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71"/>
+      <c r="A11" s="72"/>
       <c r="B11" s="30"/>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="69" t="s">
-        <v>4181</v>
-      </c>
-      <c r="B12" s="70" t="s">
-        <v>4182</v>
+      <c r="A12" s="70" t="s">
+        <v>4183</v>
+      </c>
+      <c r="B12" s="71" t="s">
+        <v>4184</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="69" t="s">
-        <v>4183</v>
-      </c>
-      <c r="B13" s="70" t="s">
-        <v>4184</v>
+      <c r="A13" s="70" t="s">
+        <v>4185</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>4186</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69" t="s">
-        <v>4185</v>
-      </c>
-      <c r="B14" s="70" t="s">
-        <v>4186</v>
+      <c r="A14" s="70" t="s">
+        <v>4187</v>
+      </c>
+      <c r="B14" s="71" t="s">
+        <v>4188</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="69" t="s">
-        <v>4187</v>
-      </c>
-      <c r="B15" s="70" t="s">
-        <v>4188</v>
+      <c r="A15" s="70" t="s">
+        <v>4189</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>4190</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="72" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>4189</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="69" t="s">
+      <c r="A17" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="70" t="s">
-        <v>4190</v>
+      <c r="B17" s="71" t="s">
+        <v>4192</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="69" t="s">
-        <v>4191</v>
-      </c>
-      <c r="B18" s="70" t="s">
-        <v>4192</v>
+      <c r="A18" s="70" t="s">
+        <v>4193</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>4194</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="72" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>4193</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="71" t="s">
-        <v>4194</v>
+      <c r="A20" s="72" t="s">
+        <v>4196</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>4195</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="s">
-        <v>4196</v>
+      <c r="A21" s="72" t="s">
+        <v>4198</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>4197</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="72"/>
+      <c r="A22" s="73"/>
       <c r="B22" s="30"/>
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="72" t="s">
         <v>176</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>4198</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="72" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>4199</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
-        <v>4200</v>
+      <c r="A25" s="72" t="s">
+        <v>4202</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>4201</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="71" t="s">
+      <c r="A26" s="72" t="s">
         <v>465</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>4202</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="71" t="s">
+      <c r="A27" s="72" t="s">
         <v>4156</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>4203</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="71" t="s">
-        <v>4204</v>
+      <c r="A28" s="72" t="s">
+        <v>4206</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>4205</v>
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="72" t="s">
+        <v>4208</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>4209</v>
       </c>
     </row>
   </sheetData>
